--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,13 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="51" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +502,41 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>access_notes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>pack_pattern_hints</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>exclude_patterns</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>last_validated</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>validation_status</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>validation_notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +571,13 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -567,6 +616,13 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -605,6 +661,13 @@
           <t>Some papers historically hosted on healthierlsc.co.uk via download_file links</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -639,6 +702,39 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Strategy: meetings-and-agendas/integrated-care-board/ lists upcoming ICB Board dates and a 'Previous Board meetings' link; each past meeting has its own sub-page with agenda/papers. Filter to ICB Board (skip ICP / committees). Pattern C; observe via nencicb-sun.icbcorporateoffice@nhs.net.</t>
+        </is>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ICB Board;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ICP;committee;Minutes only</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Landing lists ICB Board dates; papers on per-meeting sub-pages via 'Previous Board meetings'.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -673,6 +769,39 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists per-meeting entries (39 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+        </is>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=2, meeting_subpages=39.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -711,6 +840,13 @@
           <t>Papers PDFs are hosted on syics.co.uk</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -749,6 +885,39 @@
           <t>Papers hosted on wypartnership.co.uk; place-level papers also published separately by each of the 5 places (Wakefield, Leeds, Bradford, Calderdale, Kirklees)</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists per-meeting entries (27 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+        </is>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=2, meeting_subpages=27.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -795,6 +964,39 @@
           <t>Joint ICB Cluster Board with Black Country (QUA); joint pack hosted under the B&amp;S domain</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists year archives (5 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+        </is>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Board Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=5, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -841,6 +1043,13 @@
           <t>Joint ICB Cluster Board with Birmingham and Solihull (QHL); cluster pack PDFs hosted on blackcountryics.org.uk under /application/files/</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -887,6 +1096,13 @@
           <t>Joint Board Meeting in Common with Herefordshire and Worcestershire (QGH)</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -933,6 +1149,39 @@
           <t>Joint Board Meeting in Common with Coventry and Warwickshire (QWU); papers hosted on both happyhealthylives.uk and hwics.org.uk</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Strategy: /meetings/board-papers is correct and working — it lists the current meeting's papers as direct per-agenda-item PDF/spreadsheet downloads (e.g. 20 May 2026: agenda, CEO report, finance, risk), with 'Past Board Papers' for archives. Static parser undercounts because items load by agenda number. Pattern A/C.</t>
+        </is>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>agenda;CEO report;Board papers</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Working page showing 20 May 2026 papers as per-item PDFs; static parser undercounted (false no_papers_visible).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -979,6 +1228,13 @@
           <t>DLN cluster (Derby + Lincs + Notts) holds joint Boards in Common; cluster papers hosted on notts.icb.nhs.uk</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1025,6 +1281,39 @@
           <t>DLN cluster; transformation fund page at https://lincolnshire.icb.nhs.uk/transformation-fund — note the April 2026 walk-back text</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Strategy: landing surfaces board papers directly (mix of dated PDFs and/or year links). Static fetch works. Prefer the main combined board pack; filter observer notes and Q&amp;A. Pattern A/B.</t>
+        </is>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=1, meeting_subpages=6.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1071,6 +1360,13 @@
           <t>DLN cluster; hosts joint board pack PDFs at /wp-content/uploads/sites/2/</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1121,6 +1417,13 @@
           <t>LNR cluster Board in Common with Northamptonshire (QPM)</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1167,6 +1470,13 @@
           <t>LNR cluster Board in Common with LLR (QK1)</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1217,6 +1527,13 @@
           <t>Joint Board in Common with Staffs and Stoke-on-Trent (QNC)</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1267,6 +1584,13 @@
           <t>Joint Board in Common with Shropshire, Telford and Wrekin (QOC)</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1313,6 +1637,39 @@
           <t>Formed 1 April 2026 from merger of Bedfordshire, Luton and Milton Keynes (QHG, bedfordshirelutonandmiltonkeynes.icb.nhs.uk), Cambridgeshire and Peterborough (QUE, cpics.org.uk), and Hertfordshire and West Essex (QM7, hertsandwestessex.ics.nhs.uk). Predecessor sites still host historical packs.</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Strategy: landing shows a weak board-papers signal to a static parser (few dated PDFs found). Papers are likely present but loaded via JS or one click into a 'papers'/'meetings' sub-page. Confirm by following the board-papers / meetings link; prefer the main combined pack. Pattern A/C — review on next pass.</t>
+        </is>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Board Papers;Agenda and Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Validator (static) weak signal: dated_pdfs=0, year_archives=0, meeting_subpages=1; review.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1363,6 +1720,13 @@
           <t>Formed 1 April 2026 from Mid and South Essex (QH8, midandsouthessex.ics.nhs.uk) plus the North East Essex part of former Suffolk and North East Essex (QJG, suffolkandnortheastessex.icb.nhs.uk). Predecessor sites still host historical packs.</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1409,6 +1773,39 @@
           <t>Formed 1 April 2026 from Norfolk and Waveney (QMM, improvinglivesnw.org.uk) plus the Suffolk parts of former Suffolk and North East Essex (QJG, suffolkandnortheastessex.icb.nhs.uk). Predecessor sites still host historical packs.</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Strategy: landing surfaces board papers directly (mix of dated PDFs and/or year links). Static fetch works. Prefer the main combined board pack; filter observer notes and Q&amp;A. Pattern A/B.</t>
+        </is>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=0, meeting_subpages=8.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1451,6 +1848,13 @@
           <t>Single combined papers pack per board meeting</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1493,6 +1897,13 @@
           <t>Six borough place committees (Lambeth, Southwark, Lewisham, Greenwich, Bromley, Bexley) publish separately</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1531,6 +1942,39 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists year archives (3 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+        </is>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Board Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=3, meeting_subpages=3.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1581,6 +2025,13 @@
           <t>Formed 1 April 2026 from merger of North Central London (QMJ, nclhealthandcare.org.uk) and North West London (QRV, nwlondonicb.nhs.uk). Predecessor sites still host historical 'Boards in Common' packs from late 2025/early 2026.</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1623,6 +2074,13 @@
           <t>Boundary expanded 1 April 2026 to receive LSOAs transferred from former Frimley ICB (QNQ); ODS code unchanged</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1661,6 +2119,39 @@
           <t>ICB website board pack links have historically been broken; mirrors sometimes available via shepwayvox.org</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists per-meeting entries (18 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+        </is>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=0, meeting_subpages=18.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1707,6 +2198,13 @@
           <t>Formed 1 April 2026 from BOB (Buckinghamshire, Oxfordshire and Berkshire West, QU9, bucksoxonberksw.icb.nhs.uk) plus largest share of former Frimley footprint (QNQ, frimleyhealthandcare.org.uk). Predecessor sites still host historical packs.</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1753,6 +2251,39 @@
           <t>Formed 1 April 2026 from Surrey Heartlands (QXU), Sussex (QNX, sussex.ics.nhs.uk) and the Surrey parts of former Frimley (QNQ). Predecessor sites still host historical packs.</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (17 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=17, year_archives=0, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1799,6 +2330,13 @@
           <t>Loose cluster with Dorset (QVV) and Somerset (QSL) under shared chair Rob Whiteman; each has its own board</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1841,6 +2379,39 @@
           <t>Loose cluster with BSW (QOX) and Somerset (QSL); each has its own board</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Strategy: landing surfaces board papers directly (mix of dated PDFs and/or year links). Static fetch works. Prefer the main combined board pack; filter observer notes and Q&amp;A. Pattern A/B.</t>
+        </is>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=5, year_archives=1, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1883,6 +2454,13 @@
           <t>Loose cluster with BSW (QOX) and Dorset (QVV); each has its own board. Some financial decisions taken in confidential Part B.</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1929,6 +2507,13 @@
           <t>Cluster Board with Gloucestershire (QR1) from April 2026; first cluster pack pending at time of last sweep (May 2026)</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1971,6 +2556,13 @@
           <t>Cluster Board with BNSSG (QUY) from April 2026</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2021,6 +2613,13 @@
           <t>South West Peninsula joint board with Devon (QJK); cluster pack at swpboard.nhs.uk</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2071,6 +2670,13 @@
           <t>South West Peninsula joint board with Cornwall and IoS (QT6); cluster pack at swpboard.nhs.uk. Standalone Devon Board last met 28 August 2025.</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -434,7 +434,7 @@
     <col width="60" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="51" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="19" customWidth="1" min="18" max="18"/>
@@ -571,13 +571,39 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Strategy: 3-LEVEL navigation. Landing → year sub-page at /{YYYY}/ (eg /2026/) → per-meeting sub-page at /{DD-month-YYYY}/ (lowercase month, hyphen-separated, eg /29-january-2026/) → PDFs in /media/{8-char-hash}/{filename}.pdf. Multiple PDFs per meeting (full pack + Q&amp;A + presentations) — grab all. Filenames are NOT predictable (some DDMMYY, some monthYYYY, some YYYYMM) — must scrape from the DOM. Upcoming meetings sit at /get-involved/upcoming-meetings-and-events/... until archived. C&amp;M ICB publishes standalone (not a joint cluster board, despite regional cluster framing). System Primary Care Committee PDFs are a SEPARATE committee — exclude. Not JS-rendered; static HTML throughout.</t>
+        </is>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>full pack; agenda and papers; combined</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>questions and responses; presentations; System Primary Care Committee; Committee</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>16 in-window meetings via 3-level drill-down. May 2026 and March 2026 packs (4.3MB + 5.3MB) both have BAF sections — scores 87 and 367.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -966,20 +992,20 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Strategy: landing lists year archives (5 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+          <t>Strategy: landing lists year archives (5 'Board papers 20XX' year links). The year-link URLs are Concrete CMS navigate endpoints (.../navigate/13363/NNNN) that load via AJAX — static fetch returns no PDFs from the year pages. Playwright + interactive_dom strategy (render landing, click year tabs, re-scrape DOM) recovers 9 in-window meetings. PDF titles: 'ICB Board Pack {Month YYYY}' / 'Joint ICB Cluster Board Meeting - {Month YYYY}'.</t>
         </is>
       </c>
       <c r="N9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Board Papers;Public Board Pack</t>
+          <t>ICB Board Pack; Joint ICB Cluster Board Meeting; Board Papers</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Committee; Q&amp;A; Confidential; Part 2</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -989,12 +1015,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=5, meeting_subpages=0.</t>
+          <t>Year archives are Concrete CMS AJAX navigate endpoints. Playwright + click-each-year-tab required. March 2026 (16MB, BAF score 414) and May 2026 (9MB) packs recovered.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -642,13 +642,39 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Pattern A: the meetings-and-events landing page is static HTML and lists Greater Manchester Integrated Care Board meetings as dated rows, each with a 'View Agenda' link pointing directly at a combined board papers PDF in the WordPress uploads tree (https://gmintegratedcare.org.uk/wp-content/uploads/YYYY/MM/...). Each ICB Board meeting links to ONE combined papers PDF (e.g. '...integrated-care-board-papers.pdf' or '...public-combined-papers...pdf'), so no per-meeting sub-page crawl is needed. The page mixes ICB Board with other event types (ICP / committees), so filter rows to those naming the 'Integrated Care Board'. Note the upload-year folder in the URL does not always match the meeting year (a Dec 2025 pack was filed under /2026/02/).</t>
+        </is>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>wp-content/uploads/YYYY/MM/*integrated-care-board-papers*.pdf;wp-content/uploads/YYYY/MM/*combined-papers*.pdf;View Agenda link on each dated ICB Board row</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ICP;Integrated Care Partnership;Committee;Scrutiny</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Static landing page lists dated ICB Board meetings each linking a single combined papers PDF, confirmed for Nov and Dec 2025.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -730,7 +756,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Strategy: meetings-and-agendas/integrated-care-board/ lists upcoming ICB Board dates and a 'Previous Board meetings' link; each past meeting has its own sub-page with agenda/papers. Filter to ICB Board (skip ICP / committees). Pattern C; observe via nencicb-sun.icbcorporateoffice@nhs.net.</t>
+          <t>North East and North Cumbria ICB. Current landing page is correct and live; it lists upcoming ICB Board dates (16 Jun 2026, 28 Jul 2026, 29 Sep 2026) and links to per-meeting sub-pages plus a 'Previous Board meetings' archive (pattern C). The most recent held meeting (Tuesday 31 March 2026) has its own sub-page where the agenda and individual board-pack PDFs are hosted on the nencicb.nhs.uk/media/ CDN (e.g. 20260331-board-in-public-agenda.pdf). Validator's papers_partial reflects that the landing page itself surfaces only one meeting sub-page rather than dated PDFs; the per-meeting sub-page resolves to the full pack. This is the ICB Board, not ICP or a committee.</t>
         </is>
       </c>
       <c r="N5" t="b">
@@ -738,27 +764,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ICB Board;Agenda and Papers</t>
+          <t>/board-meeting-held-in-public-on-{day}-{month}-{year}/;nencicb.nhs.uk/media/&lt;id&gt;/&lt;YYYYMMDD&gt;-board-in-public-agenda.pdf;/previous-board-meetings/</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ICP;committee;Minutes only</t>
+          <t>ICP;Integrated Care Partnership;Committee;Place</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Landing lists ICB Board dates; papers on per-meeting sub-pages via 'Previous Board meetings'.</t>
+          <t>31 March 2026 ICB Board meeting sub-page resolves to a full set of dated board-pack PDFs on the nencicb.nhs.uk media CDN.</t>
         </is>
       </c>
     </row>
@@ -1122,13 +1148,39 @@
           <t>Joint Board Meeting in Common with Herefordshire and Worcestershire (QGH)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Coventry and Warwickshire ICB. The current URL is correct and live, but the happyhealthylives.uk host returns HTTP 403 to plain WebFetch (anti-bot, pattern E), which is why the validator flagged it broken. Loaded successfully under Playwright (location.host=www.happyhealthylives.uk): the page is a shared NHS Coventry &amp; Warwickshire / Herefordshire &amp; Worcestershire ICB Board site and renders current 2026 ICB Board content (CWHW ICB Board Governance Log 2026-27, draft public minutes 18 March 2026, 21 January 2026 papers). Per-meeting 'Meeting Papers' / agenda items are JS-driven accordions (anchors are href='#'); the underlying PDFs/xlsx live under /download/clientfiles/files/ and require JS expansion, so this is also pattern D (JS-needs-Playwright). This is the ICB Board (skip the separate ICP Meetings page). For HSJ purposes the CW and HW ICBs share this board infrastructure.</t>
+        </is>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>/download/clientfiles/files/Agenda%20&lt;NN&gt;%20CWHW%20...pdf;/download/clientfiles/files/...Governance%20Log%20&lt;YYYY-YY&gt;.xlsx;JS accordion 'Meeting Papers (part 1/2/3)' under each meeting date</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>ICP;ICP Meetings;Integrated Care Partnership;Committee;CAMHS Commissioning</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Page is 403 to WebFetch but loads in Playwright showing live 2026 CWHW ICB Board papers (Governance Log 2026-27, 18 March 2026 minutes); pack PDFs sit behind JS accordions.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1177,7 +1229,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Strategy: /meetings/board-papers is correct and working — it lists the current meeting's papers as direct per-agenda-item PDF/spreadsheet downloads (e.g. 20 May 2026: agenda, CEO report, finance, risk), with 'Past Board Papers' for archives. Static parser undercounts because items load by agenda number. Pattern A/C.</t>
+          <t>Herefordshire and Worcestershire ICB. Current URL is correct and live; it shows the latest ICB Board meeting (Wednesday 20 May 2026) with ~9 documents (agenda &amp; governance log, draft minutes 18 March 2026, CEO report, delivery &amp; quality, financial plan, BAF, escalation reports). Validator's no_papers_visible appears to be a render/short-text miss. A 'Past Board Papers' sub-page (/meetings/past-board-papers) lists prior 2025-26 meetings, with the individual PDFs served from the hwics.org.uk/download_file/ CDN (pattern A/C: dated meeting groupings each linking per-item PDFs). This is the ICB Board, not ICP/committee.</t>
         </is>
       </c>
       <c r="N12" t="b">
@@ -1185,17 +1237,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>agenda;CEO report;Board papers</t>
+          <t>/meetings/board-papers (latest meeting);/meetings/past-board-papers (archive);https://www.hwics.org.uk/download_file/&lt;id&gt;/463 per-item PDFs</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>ICP;Integrated Care Partnership;Committee</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1205,7 +1257,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Working page showing 20 May 2026 papers as per-item PDFs; static parser undercounted (false no_papers_visible).</t>
+          <t>Landing page lists 20 May 2026 ICB Board pack (9 docs) and a past-board-papers archive back through 2025 with per-item PDFs on the hwics.org.uk CDN.</t>
         </is>
       </c>
     </row>
@@ -1254,13 +1306,39 @@
           <t>DLN cluster (Derby + Lincs + Notts) holds joint Boards in Common; cluster papers hosted on notts.icb.nhs.uk</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Derby and Derbyshire ICB. Current landing URL is correct and live; it lists ICB Board dates (now operating as the DLN cluster Board-in-Common: 19 Mar 2026, 21 May 2026, 16 Jul 2026, etc.) and links to a dedicated 'Meeting papers' archive page. That archive (integrated-care-board-meeting-papers/) holds dated PDF packs as /download/ links by fiscal year (pattern C, single combined pack per meeting), e.g. 'DLN ICB Board Papers 21 May 2026' and the 15 Jan 2026 agenda + papers. Validator's no_papers_visible reflects that the packs sit on the linked meeting-papers sub-page rather than the landing page. Note Derby &amp; Derbyshire now sits in the Derby/Lincolnshire/Nottingham (DLN) cluster, so recent packs are DLN cluster Board-in-Common documents; some summary/joint material may also be cross-published on the partner notts.icb.nhs.uk domain, but the full Derbyshire-hosted packs are on joinedupcarederbyshire.co.uk. This is the ICB Board, not ICP/committee.</t>
+        </is>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>/derbyshire-integrated-care-board/integrated-care-board-meeting-papers/ (archive);/download/dln-icb-board-papers-&lt;dd-month-yyyy&gt;/;/download/icb-board-papers-for-board-meeting-in-public-&lt;dd-month-yyyy&gt;/;prefer combined 'ICB Board Papers' pack over separate agenda</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>ICP;Integrated Care Partnership;Committee;Ratified Minutes of ICB Committee Meetings</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Meeting-papers archive holds dated combined PDF packs including 'DLN ICB Board Papers 21 May 2026' and 15 January 2026 agenda + board papers.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1386,13 +1464,39 @@
           <t>DLN cluster; hosts joint board pack PDFs at /wp-content/uploads/sites/2/</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Pattern A/C combined: the ICB Board landing page lists every meeting by date and links a single combined Agenda+Papers PDF per meeting directly on the landing (no separate year-archive pages needed). Confirmed dated DLN/NNICB ICB Board PDFs are present for 14 May 2025, 9 Jul 2025, 10 Sep 2025, 20 Nov 2025, 15 Jan 2026, 19 Mar 2026 and 21 May 2026, plus a forward schedule of future 2026/27 dates. This is the Derbyshire-Leicester-Nottingham (DLN) cluster board served on Nottingham and Nottinghamshire ICB's own domain; PDFs are prefixed DLN-ICB-Board or NNICB-Board. Take the largest combined board-papers PDF per meeting.</t>
+        </is>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>DLN-ICB-Board;NNICB-Board;ICB-Public-Board-papers;ICB-Board-DD.MM.YY.pdf;wp-content/uploads/sites/2/</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Cluster-Board-Meeting-Summary;Committee;ICP Board;Audit</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Landing page directly lists dated 2025-2026 ICB Board paper PDFs per meeting, no further navigation required.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1473,7 +1577,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.icnorthamptonshire.org.uk/icbboardmeetings/</t>
+          <t>https://www.icnorthamptonshire.org.uk/documents?media_folder=2078&amp;root_folder=Public%20Board%20and%20Committee%20Meeting%20papers%20-%20ICB</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1496,13 +1600,39 @@
           <t>LNR cluster Board in Common with LLR (QK1)</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Pattern B/F: the configured /icbboardmeetings landing only lists upcoming meeting dates and event sub-pages with no published PDFs ('Papers will be available nearer the date'), so the working URL is the document-library 'Public Board and Committee Meeting papers - ICB' repository on the ICB's own domain. It exposes per-year folders (ICB Board papers 2022/2023/2024/2025/2026); the 2026 folder (media_folder=2899) holds dated combined PDFs. NOTE: these are joint 'LLR ICB &amp; NICB Board meeting in common' packs for the Leicester-Northamptonshire-Rutland (LNR) cluster, legitimately hosted on Northamptonshire ICB's own domain (icnorthamptonshire.org.uk) via download.cfm links. Take the largest combined PUBLIC papers PDF per meeting and filter the repository to the ICB Board year folders, not committee papers.</t>
+        </is>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>LLR &amp; NICB Board meeting in Common;Board meetings in common PUBLIC papers;download.cfm?doc=;ICB Board papers 2026;media_folder=2899</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Committee;ICP Board;Audit;Remuneration;Finance Committee;Quality Committee</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Document-library ICB Board year folders list dated joint LLR &amp; NICB board-in-common public papers for Feb, Mar and Apr 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1530,36 +1660,62 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
+          <t>https://www.shropshiretelfordandwrekin.nhs.uk/about-us/how-we-are-run/meetings-committees-and-events/governing-body-meetings/previous-board-meetings/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.shropshiretelfordandwrekin.nhs.uk</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>STW-SSOT</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>https://www.shropshiretelfordandwrekin.nhs.uk/about-us/how-we-are-run/meetings-committees-and-events/governing-body-meetings/</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>https://www.shropshiretelfordandwrekin.nhs.uk</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>STW-SSOT</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>https://www.shropshiretelfordandwrekin.nhs.uk/about-us/how-we-are-run/meetings-committees-and-events/governing-body-meetings/</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>Joint Board in Common with Staffs and Stoke-on-Trent (QNC)</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Pattern A/F: the configured governing-body-meetings landing only shows the forward meeting schedule with no PDFs, so the working URL is its 'Previous Board Meetings' child page, which lists every past meeting by date with directly-linked Agenda Papers (plus separate Appendices and Public Questions PDFs) on the ICB's own domain. NOTE: from 2026 these are joint 'NHS STW &amp; SSOT Board in Common' / 'Integrated Care Board' packs covering the Shropshire-Telford-Wrekin and Staffordshire-Stoke (STW-SSOT) cluster, hosted on STW ICB's own domain (a few older 2025 files sit on the partner shroandtel.co.uk domain). Take the largest combined Agenda Papers PDF and pair it with the Appendices pack for the same date; skip standalone Public Questions and committee files.</t>
+        </is>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NHS-STW-SSOT-Board-in-Common-Agenda-Papers;NHS-STW-Integrated-Care-Board-Agenda-Papers;Combined-Papers_STW-Board;Appendices-Pack;wp-content/uploads/</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Public-Questions;questions-from-members-of-public;Committee;ICP;Appendices (when a combined pack exists)</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Previous Board Meetings page lists dated ICB Board / Board-in-Common agenda paper PDFs through April 2026 with recordings.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1610,13 +1766,39 @@
           <t>Joint Board in Common with Shropshire, Telford and Wrekin (QOC)</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Pattern B + C: the board-papers landing is a static document library exposing year folders (/board-papers/2025/, /board-papers/2026/). Each year folder lists month sub-folders (e.g. /2025/november-2025/), and each month folder contains a single combined ICB Board pack file accessed via a '...?layout=file' download URL (e.g. .../november-2025/icb-board-meeting-papers-20-november-2025/?layout=file -&gt; 'COMBINED PAPERS ICB Board Meeting ... PUBLIC Session.pdf', ~6 MB). Crawl: year folder -&gt; month folder -&gt; pick the item titled 'ICB Board Meeting Papers &lt;date&gt;' and append ?layout=file. Month folders also contain unrelated items (Easy Read letters, event flyers), so prefer the combined ICB Board papers item only; this is the ICB Board collection, separate from Board briefings and committee collections.</t>
+        </is>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>/board-papers/YYYY/ -&gt; month sub-folder;/board-papers/YYYY/&lt;month&gt;-YYYY/icb-board-meeting-papers-&lt;date&gt;/?layout=file;title 'ICB Board Meeting Papers &lt;date&gt;' = combined COMBINED PAPERS PUBLIC Session PDF</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Board briefings;Committee;Easy Read Letter;event;Clinical Professional Leadership</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Year-&gt;month folder structure confirmed; November 2025 month folder yields one combined ICB Board papers PDF (~6.44 MB) via the ?layout=file URL.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1648,7 +1830,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.hertsandwestessex.ics.nhs.uk/about/icb/board/</t>
+          <t>https://www.hertsandwestessex.ics.nhs.uk/documents/?location=all&amp;type=board-papers&amp;cat=all&amp;date=</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1665,7 +1847,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Strategy: landing shows a weak board-papers signal to a static parser (few dated PDFs found). Papers are likely present but loaded via JS or one click into a 'papers'/'meetings' sub-page. Confirm by following the board-papers / meetings link; prefer the main combined pack. Pattern A/C — review on next pass.</t>
+          <t>Pattern C/F: the configured /about/icb/board/ landing only links to members and a meetings-in-public overview with no dated PDFs, so the working URL is the board-papers document archive (type=board-papers), which lists one per-meeting document page per ICB Board meeting in public on the org's own domain. Each per-meeting page (slug 'papers-for-the-integrated-care-board-meeting-in-public-&lt;weekday&gt;-&lt;date&gt;') holds that meeting's pack. NOTE: this org is recorded under the new Central East ICB ODS code (S1Y5D) but still publishes on its legacy Herts and West Essex ICS domain (hertsandwestessex.ics.nhs.uk); the board moved from bi-monthly to quarterly from April 2025, so meetings are sparse (latest 6 Feb 2026). Use the per-meeting document page as the meeting URL and take the combined board pack; exclude Primary Care Transformation Committee papers.</t>
         </is>
       </c>
       <c r="N20" t="b">
@@ -1673,27 +1855,27 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Board Papers;Agenda and Papers;Public Board Pack</t>
+          <t>papers-for-the-integrated-care-board-meeting-in-public;/documents/;ICB Board category</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Primary Care Transformation;Committee;ICP;AGM</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Validator (static) weak signal: dated_pdfs=0, year_archives=0, meeting_subpages=1; review.</t>
+          <t>Board-papers archive lists dated ICB-Board-categorised meeting packs through 6 February 2026 on the org's own domain.</t>
         </is>
       </c>
     </row>
@@ -1746,13 +1928,39 @@
           <t>Formed 1 April 2026 from Mid and South Essex (QH8, midandsouthessex.ics.nhs.uk) plus the North East Essex part of former Suffolk and North East Essex (QJG, suffolkandnortheastessex.icb.nhs.uk). Predecessor sites still host historical packs.</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>The current Publications landing page is live on the org's own domain and is the correct route to Essex ICB Board papers (pattern C, leading to per-meeting sub-pages). Filtering the publications list by type 'Board papers - ICB Board Meeting Papers' surfaces per-meeting entries such as 'Essex ICB Board Meeting Pack 23 April 2026', whose sub-page links a single combined Part 1 board pack PDF (https://www.essex.icb.nhs.uk/wp-content/uploads/2026/04/Part-1-Essex-ICB-Board-Meeting-Pack-23-April-2026.pdf). The landing itself shows no dated PDFs directly (hence the validator's papers_partial), but a one-click meeting sub-page reaches the dated 2026 ICB Board pack. Skip ICP and committee entries in the same publications list; prefer the largest combined Part 1 pack PDF.</t>
+        </is>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>/publications/essex-icb-board-meeting-pack-{DD-month-YYYY}/;wp-content/uploads/{YYYY}/{MM}/Part-1-Essex-ICB-Board-Meeting-Pack-*.pdf</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Integrated Care Partnership;ICP;Committee;Quality Committee;Finance Committee</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Per-meeting sub-page off the publications list links a combined Part 1 Essex ICB Board pack PDF dated 23 April 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1859,7 +2067,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://northeastlondon.icb.nhs.uk/board-meetings/</t>
+          <t>https://northeastlondon.icb.nhs.uk/about-us/about-nhs-north-east-london/our-board/board-meetings-and-papers/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1874,13 +2082,39 @@
           <t>Single combined papers pack per board meeting</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>The previously stored URL (/board-meetings/) is a generic meetings calendar that mixes ICP, primary-care sub-committees and place-based partnership boards, which is why the validator saw no ICB Board papers. The correct dedicated NEL ICB Board landing on the org's own domain is /about-us/about-nhs-north-east-london/our-board/board-meetings-and-papers/ (pattern C, wrong-url-fixed). It lists ICB Board meetings (every other month) as per-meeting sub-pages; each past meeting sub-page carries the dated combined board pack via /download-attachment/{id} links, and direct dated PDFs also exist under wp-content/uploads (e.g. NHS-North-East-London-ICB-Board-29.01.2025.pdf). Upcoming meetings show papers a minimum of five working days before; future-dated sub-pages have no PDFs yet. Filter to the NEL ICB Board only; skip ICP, sub-committees and partnership/place boards.</t>
+        </is>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>/board-meetings/north-east-london-icb-board-meeting-{n}/;/download-attachment/{id};wp-content/uploads/{YYYY}/{MM}/NHS-North-East-London-ICB-Board-{DD.MM.YYYY}.pdf</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Integrated Care Partnership;ICP;Sub-committee;Primary Care Contracts;Partnership Board;Health &amp; Wellbeing Board;Tower Hamlets Together</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Confirmed dated 2025 NEL ICB Board pack PDF (29 January 2025) on the org's own domain reachable from the board landing's per-meeting structure.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2051,13 +2285,39 @@
           <t>Formed 1 April 2026 from merger of North Central London (QMJ, nclhealthandcare.org.uk) and North West London (QRV, nwlondonicb.nhs.uk). Predecessor sites still host historical 'Boards in Common' packs from late 2025/early 2026.</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>West and North London ICB is a newly created organisation (live from 1 April 2026, formed from the North West London and North Central London ICBs), so the earliest ICB Board pack is the 1 April 2026 inaugural meeting. The stored board-meetings page is the correct ICB Board landing on the org's own domain, but the actual packs live in a JavaScript-rendered document library (pattern D, needs Playwright) under /how-we-are-run/policies-and-publications/navigate/479/2410, organised into per-meeting date folders. The 1 April 2026 folder (navigate/480/2410) was confirmed to contain the ICB Board meeting-in-public agenda plus supporting papers as download_file links on the org's own domain. The board landing page itself only lists meeting dates and notes papers appear about a week before each meeting, which is why the validator saw no papers. Filter to the W&amp;NL ICB Board; legacy NWL/NCL papers are linked off-site on partner ICB domains (nwlondonicb.nhs.uk, nclhealthandcare.org.uk) for pre-merger history.</t>
+        </is>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>/how-we-are-run/policies-and-publications/navigate/{folderId}/2410#document-library-2410;/download_file/{uuid}/293</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>North West London ICB (legacy);North Central London ICB (legacy);Committee;ICP;Integrated Care Partnership</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Playwright confirmed the 1 April 2026 W&amp;NL ICB Board meeting-in-public agenda and supporting papers as download_file links in the JS document library on the org's own domain.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2100,13 +2360,39 @@
           <t>Boundary expanded 1 April 2026 to receive LSOAs transferred from former Frimley ICB (QNQ); ODS code unchanged</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Pattern C: the integrated-care-board-meetings landing is static HTML listing dated ICB Board meetings, each linking to a per-meeting sub-page of the form /icb/integrated-care-board-meetings/navigate/23515/&lt;id&gt;. Each per-meeting page does NOT offer a single combined pack; instead it lists numbered individual paper PDFs (Paper 0 Agenda, Paper 2a Minutes, Paper 4 Chair report, Paper 5 CEO report, Paper 6 BAF, etc.), each downloaded via /download_file/&lt;file-id&gt;/452. To assemble a full pack a crawler must follow each meeting page and fetch all Paper N download_file links (the agenda is 'Paper 0 - Public Agenda'). The /navigate/23515/ branch is the ICB Board; skip other committee/ICP listings.</t>
+        </is>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>/icb/integrated-care-board-meetings/navigate/23515/&lt;id&gt; per-meeting page;/download_file/&lt;file-id&gt;/452 for each numbered paper PDF;agenda = 'Paper 0 - Public Agenda'; collect all Paper N PDFs (no combined pack)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>ICP;Integrated Care Partnership;Committee;Confidential;Private</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Per-meeting page for 5 November 2025 confirmed listing ~19 individual numbered paper PDFs via /download_file/ links; no single combined pack is published.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2209,7 +2495,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.thamesvalley.icb.nhs.uk/policies-and-documents/how-we-make-decisions/board-papers/</t>
+          <t>https://www.thamesvalley.icb.nhs.uk/policies-and-documents/how-we-make-decisions/board-papers/nhs-thames-valley-icb</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2224,13 +2510,39 @@
           <t>Formed 1 April 2026 from BOB (Buckinghamshire, Oxfordshire and Berkshire West, QU9, bucksoxonberksw.icb.nhs.uk) plus largest share of former Frimley footprint (QNQ, frimleyhealthandcare.org.uk). Predecessor sites still host historical packs.</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>The previously stored board-papers parent page is an empty container that only shows two section headers ('NHS Thames Valley ICB' and 'Pre-NHS Thames Valley archive') with no documents, which is why the validator saw 347 chars of text and no papers. The correct live sub-page is /policies-and-documents/how-we-make-decisions/board-papers/nhs-thames-valley-icb (wrong-url-fixed, pattern A: dated combined pack on the landing), which lists the dated Thames Valley ICB Board papers, including 'Thames Valley ICB Board papers 20 May 2026' as a single combined ~2.8MB PDF served via a /file download path on the org's own domain. Skip the 'Pre-NHS Thames Valley archive' (legacy predecessor ICB papers) and any committee/ICP items.</t>
+        </is>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>/policies-and-documents/how-we-make-decisions/board-papers/nhs-thames-valley-icb/{id}-thames-valley-icb-board-papers-{dd-month-yyyy}/file</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Pre-NHS Thames Valley archive;Committee;ICP;Integrated Care Partnership</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>The nhs-thames-valley-icb sub-page lists a dated combined Thames Valley ICB Board pack PDF for 20 May 2026 on the org's own domain.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2533,13 +2845,39 @@
           <t>Cluster Board with Gloucestershire (QR1) from April 2026; first cluster pack pending at time of last sweep (May 2026)</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Pattern C: the /events/ listing is static HTML and includes dated 'Integrated Care Board (ICB) Board meeting &lt;date&gt;' events, each linking to a per-event sub-page (/events/integrated-care-board-icb-board-meeting-&lt;date&gt;/). The event page does NOT provide a single combined pack; it lists the agenda PDFs (e.g. '00 - Agenda ICB Board Open ...') plus ~14 individual supporting paper/committee report PDFs, all hosted under bnssghealthiertogether.org.uk/wp-content/uploads/YYYY/MM/. Crawl: filter /events/ to titles containing 'ICB Board meeting' (skip ICP and standalone committee events), open the event page, then collect the '00 - Agenda ICB Board Open' PDF and all wp-content/uploads paper PDFs. Note some 2026 entries are 'Joint Cluster' ICB Board meetings.</t>
+        </is>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>/events/integrated-care-board-icb-board-meeting-&lt;date&gt;/ per-event page;wp-content/uploads/YYYY/MM/00-Agenda-ICB-Board-Open-*.pdf (agenda);wp-content/uploads/YYYY/MM/*.pdf individual supporting papers (no combined pack)</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>ICP;Integrated Care Partnership;Committee;Annual General Meeting</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Per-event page for 4 December 2025 confirmed listing open/motion agenda PDFs plus ~14 individual supporting paper PDFs under wp-content/uploads; no single combined pack.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2639,13 +2977,39 @@
           <t>South West Peninsula joint board with Devon (QJK); cluster pack at swpboard.nhs.uk</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Pattern D (JS-rendered). A static fetch of the 'Meetings in public' page returns a near-empty body; under headless Chromium it renders on cios.icb.nhs.uk (verify location.host — the shared browser drifts to other workers' pages) at ~4KB of content and exposes the ICB Board papers. The page surfaces (a) direct dated ICB Board PDFs for the current FY hosted on a SEPARATE document-library subdomain docs.cios.icb.nhs.uk, and (b) per-FY year-archive sub-pages /about/meetings/2025-to-2026-papers/, /2024-to-2025-papers/, /2023-to-2024-papers/, /2022-to-2023-papers/. The 2025-to-2026-papers archive page (also JS-rendered) lists each ICB Board meeting's papers itemised per agenda item (NOT a single combined pack) at docs.cios.icb.nhs.uk/DocumentsLibrary/NHSCornwallAndIslesOfScilly/Organisation/PublicMeetings/BoardMeetings/{FY}/{YYYYMM}/ (FY = 2526, YYYYMM = meeting month), e.g. AgendaPart1ICBBoardMay2025.pdf and ICB{seq}*.pdf reports. A crawler should anchor each meeting on the 'Agenda Part 1 ICB Board {Month} {Year}' PDF and gather the sibling ICB{seq} files in the same {YYYYMM} folder. Some links are wrapped in Outlook safelinks redirects (unwrap via url= param). Static fetch misses all of this. Filter to the ICB Board only — EXCLUDE the Integrated Care Partnership (/ics/icp/) and the South West Peninsula ICB-cluster page (/icb-cluster/).</t>
+        </is>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>/about/meetings/{YYYY}-to-{YYYY}-papers/ year-archive sub-pages;docs.cios.icb.nhs.uk/DocumentsLibrary/NHSCornwallAndIslesOfScilly/Organisation/PublicMeetings/BoardMeetings/{FY}/{YYYYMM}/*.pdf;anchor meeting on AgendaPart1ICBBoard{Month}{Year}.pdf, gather sibling ICB{seq}*.pdf in same folder;FY folder is 4-digit (2526); papers are itemised per agenda item, not one combined pack;unwrap gbr01.safelinks.protection.outlook.com via url= query parameter</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>/ics/icp/ (Integrated Care Partnership);/icb-cluster/ (South West Peninsula ICB cluster board);BoardQuestionsAndSupportingInformation (public questions, not board packs);youtube.com playlist links;language/translate anchors (#)</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>The 2025-to-2026 archive rendered dated ICB Board papers for May 2025, July 2025 and an Extraordinary meeting (Aug 2025 / May 2026) under BoardMeetings/2526/{YYYYMM}/ on docs.cios.icb.nhs.uk, distinct from ICP/committee content.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -756,7 +756,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>North East and North Cumbria ICB. Current landing page is correct and live; it lists upcoming ICB Board dates (16 Jun 2026, 28 Jul 2026, 29 Sep 2026) and links to per-meeting sub-pages plus a 'Previous Board meetings' archive (pattern C). The most recent held meeting (Tuesday 31 March 2026) has its own sub-page where the agenda and individual board-pack PDFs are hosted on the nencicb.nhs.uk/media/ CDN (e.g. 20260331-board-in-public-agenda.pdf). Validator's papers_partial reflects that the landing page itself surfaces only one meeting sub-page rather than dated PDFs; the per-meeting sub-page resolves to the full pack. This is the ICB Board, not ICP or a committee.</t>
+          <t>This is the correct live ICB Board landing (title 'ICB Board meetings | North East and North Cumbria NHS'). It is static-fetchable but does NOT hold PDFs directly, it is an index that lists upcoming meeting dates and links to one per-meeting sub-page for the most recent meeting plus a 'Previous Board meetings' archive. To reach current dated papers, follow the dated sub-page link (e.g. /board-meeting-held-in-public-on-tuesday-31-march-2026/), which contains the full PDF set (agenda, CEO report, finance, IDR, committee highlight reports) hosted under /media/&lt;hash&gt;/&lt;item&gt;.pdf. Crawler: fetch this landing, extract the dated sub-page(s) and the /previous-board-meetings/ page, then harvest the /media/*.pdf links on each. Coverage current (latest 31 Mar 2026; upcoming 16 Jun, 28 Jul, 29 Sep 2026). Filter out the separate ICP meetings link.</t>
         </is>
       </c>
       <c r="N5" t="b">
@@ -764,17 +764,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>/board-meeting-held-in-public-on-{day}-{month}-{year}/;nencicb.nhs.uk/media/&lt;id&gt;/&lt;YYYYMMDD&gt;-board-in-public-agenda.pdf;/previous-board-meetings/</t>
+          <t>/media/;board-in-public-agenda;ceo_board_report;icb-board;-board-march;item-</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ICP;Integrated Care Partnership;Committee;Place</t>
+          <t>integrated-care-partnership;icp;-icp-</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>31 March 2026 ICB Board meeting sub-page resolves to a full set of dated board-pack PDFs on the nencicb.nhs.uk media CDN.</t>
+          <t>Landing indexes a dated sub-page (31 March 2026) carrying a full set of board PDFs under /media/.</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Herefordshire and Worcestershire ICB. Current URL is correct and live; it shows the latest ICB Board meeting (Wednesday 20 May 2026) with ~9 documents (agenda &amp; governance log, draft minutes 18 March 2026, CEO report, delivery &amp; quality, financial plan, BAF, escalation reports). Validator's no_papers_visible appears to be a render/short-text miss. A 'Past Board Papers' sub-page (/meetings/past-board-papers) lists prior 2025-26 meetings, with the individual PDFs served from the hwics.org.uk/download_file/ CDN (pattern A/C: dated meeting groupings each linking per-item PDFs). This is the ICB Board, not ICP/committee.</t>
+          <t>The current URL IS correct and DOES surface dated board papers (title 'Board papers :: Herefordshire and Worcestershire Integrated Care System'); the validator's 1691-char read was a transient/partial render. The page shows only the NEXT/most-recent meeting (Wednesday 20 May 2026) with its agenda and item PDFs; the historical archive lives at the sibling page /meetings/past-board-papers (18 Mar 2026, 21 Jan 2026, 19 Nov 2025...). The actual document files are NOT on the icb.nhs.uk domain, they are served from the ICS document store at www.hwics.org.uk/download_file/&lt;id&gt;/463. Crawler should fetch both /meetings/board-papers (current) and /meetings/past-board-papers (archive) and harvest the hwics.org.uk/download_file links. Prefer the 'Agenda 00 Public Board &lt;date&gt;' PDF as the anchor. Papers may be branded 'CWHW' cluster but are still the H&amp;W ICB Board; do not confuse with the ICP or committee items.</t>
         </is>
       </c>
       <c r="N12" t="b">
@@ -1237,17 +1237,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>/meetings/board-papers (latest meeting);/meetings/past-board-papers (archive);https://www.hwics.org.uk/download_file/&lt;id&gt;/463 per-item PDFs</t>
+          <t>hwics.org.uk/download_file/;Agenda 00 Public Board;CEO report;Public Board;Finance Plan</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ICP;Integrated Care Partnership;Committee</t>
+          <t>partnership;icp;Committee Escalation</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Landing page lists 20 May 2026 ICB Board pack (9 docs) and a past-board-papers archive back through 2025 with per-item PDFs on the hwics.org.uk CDN.</t>
+          <t>Current URL surfaces the 20 May 2026 board pack; full archive at /meetings/past-board-papers, files hosted on hwics.org.uk.</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://joinedupcarederbyshire.co.uk/derbyshire-integrated-care-board/integrated-care-board-meetings/</t>
+          <t>https://joinedupcarederbyshire.co.uk/derbyshire-integrated-care-board/integrated-care-board-meeting-papers/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Derby and Derbyshire ICB. Current landing URL is correct and live; it lists ICB Board dates (now operating as the DLN cluster Board-in-Common: 19 Mar 2026, 21 May 2026, 16 Jul 2026, etc.) and links to a dedicated 'Meeting papers' archive page. That archive (integrated-care-board-meeting-papers/) holds dated PDF packs as /download/ links by fiscal year (pattern C, single combined pack per meeting), e.g. 'DLN ICB Board Papers 21 May 2026' and the 15 Jan 2026 agenda + papers. Validator's no_papers_visible reflects that the packs sit on the linked meeting-papers sub-page rather than the landing page. Note Derby &amp; Derbyshire now sits in the Derby/Lincolnshire/Nottingham (DLN) cluster, so recent packs are DLN cluster Board-in-Common documents; some summary/joint material may also be cross-published on the partner notts.icb.nhs.uk domain, but the full Derbyshire-hosted packs are on joinedupcarederbyshire.co.uk. This is the ICB Board, not ICP/committee.</t>
+          <t>joinedupcarederbyshire.co.uk IS the current, correct Derby &amp; Derbyshire ICB site (confirmed live, 2026 content). The flagged URL (/integrated-care-board-meetings/) is the schedule/dates page and only links one stray PDF, hence 'no papers visible'. The actual papers archive is the SIBLING page /derbyshire-integrated-care-board/integrated-care-board-meeting-papers/ (title 'Integrated Care Board meeting papers'), which lists every meeting 2020-2026 with download links. Papers are served via WordPress Download Manager pretty-URLs of the form /download/&lt;slug&gt;/ that 302-redirect to the actual PDF on the same domain. Static-fetchable. Since the DLN cluster (Derbyshire/Lincolnshire/Nottinghamshire) formed, recent packs are joint 'DLN ICB Board'/'Board meeting in common' documents, these ARE the Derbyshire ICB board papers (each ICB remains a separate legal entity and publishes the same pack on its own site). Crawler: index the meeting-papers page and follow /download/&lt;slug&gt;/ links. Prefer the 'DLN ICB Board Papers &lt;date&gt;' pack. Exclude ICP and committee-minutes links.</t>
         </is>
       </c>
       <c r="N13" t="b">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>/derbyshire-integrated-care-board/integrated-care-board-meeting-papers/ (archive);/download/dln-icb-board-papers-&lt;dd-month-yyyy&gt;/;/download/icb-board-papers-for-board-meeting-in-public-&lt;dd-month-yyyy&gt;/;prefer combined 'ICB Board Papers' pack over separate agenda</t>
+          <t>/download/;dln-icb-board-papers;ddicb-board-meeting-in-public-meeting-pack;icb-board-agenda;DLN-ICB-Board;wpdmdl=</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>ICP;Integrated Care Partnership;Committee;Ratified Minutes of ICB Committee Meetings</t>
+          <t>partnership;icp;committee-minutes;ratified-minutes</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Meeting-papers archive holds dated combined PDF packs including 'DLN ICB Board Papers 21 May 2026' and 15 January 2026 agenda + board papers.</t>
+          <t>Sibling 'meeting-papers' page lists full 2025-2026 DLN/DDICB board packs via /download/ redirects to PDFs on the same domain.</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Pattern A/C combined: the ICB Board landing page lists every meeting by date and links a single combined Agenda+Papers PDF per meeting directly on the landing (no separate year-archive pages needed). Confirmed dated DLN/NNICB ICB Board PDFs are present for 14 May 2025, 9 Jul 2025, 10 Sep 2025, 20 Nov 2025, 15 Jan 2026, 19 Mar 2026 and 21 May 2026, plus a forward schedule of future 2026/27 dates. This is the Derbyshire-Leicester-Nottingham (DLN) cluster board served on Nottingham and Nottinghamshire ICB's own domain; PDFs are prefixed DLN-ICB-Board or NNICB-Board. Take the largest combined board-papers PDF per meeting.</t>
+          <t>This is the correct, fully-populated Nottingham &amp; Nottinghamshire ICB Board page (title 'Our Board - NHS Nottingham and Nottinghamshire ICB'). Static-fetchable; lists every 2025-2026 meeting with direct 'Agenda and Papers' PDF links hosted on the same domain at /wp-content/uploads/sites/2/&lt;yyyy&gt;/&lt;mm&gt;/...pdf. The validator saw only 1 dated PDF likely due to lazy-loaded accordions, but a full fetch reveals the complete index (21 May 2026, 19 Mar 2026, 15 Jan 2026, 20 Nov 2025, 10 Sep 2025, 9 Jul 2025, 14 May 2025). Recent packs are named 'DLN-ICB-Board-&lt;date&gt;.pdf' reflecting the Derbyshire/Lincolnshire/Nottinghamshire cluster 'board meeting in common'; these are the Notts ICB board papers. Crawler: fetch this page and harvest the /wp-content/uploads/.../*.pdf links; prefer the 'DLN-ICB-Board-papers-&lt;date&gt;.pdf'/'ICB-Board-&lt;date&gt;.pdf' pack and the 'Cluster-Board-Meeting-Summary' for the readout. Exclude ICP and committee links.</t>
         </is>
       </c>
       <c r="N15" t="b">
@@ -1474,17 +1474,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>DLN-ICB-Board;NNICB-Board;ICB-Public-Board-papers;ICB-Board-DD.MM.YY.pdf;wp-content/uploads/sites/2/</t>
+          <t>/wp-content/uploads/sites/2/;DLN-ICB-Board;NNICB-Board;ICB-Board-;ICB-Public-Board-papers;Cluster-Board-Meeting-Summary</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Cluster-Board-Meeting-Summary;Committee;ICP Board;Audit</t>
+          <t>partnership;icp;committee;healthandcarenotts.co.uk</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Landing page directly lists dated 2025-2026 ICB Board paper PDFs per meeting, no further navigation required.</t>
+          <t>Page is a full board-papers index with direct dated PDF links for all 2025-2026 meetings on the same domain.</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The current Publications landing page is live on the org's own domain and is the correct route to Essex ICB Board papers (pattern C, leading to per-meeting sub-pages). Filtering the publications list by type 'Board papers - ICB Board Meeting Papers' surfaces per-meeting entries such as 'Essex ICB Board Meeting Pack 23 April 2026', whose sub-page links a single combined Part 1 board pack PDF (https://www.essex.icb.nhs.uk/wp-content/uploads/2026/04/Part-1-Essex-ICB-Board-Meeting-Pack-23-April-2026.pdf). The landing itself shows no dated PDFs directly (hence the validator's papers_partial), but a one-click meeting sub-page reaches the dated 2026 ICB Board pack. Skip ICP and committee entries in the same publications list; prefer the largest combined Part 1 pack PDF.</t>
+          <t>The /publications/ index is the correct landing but does not list dated PDFs directly; it links to per-meeting publication sub-pages titled 'Essex ICB Board Meeting Pack &lt;date&gt;' (e.g. /publications/essex-icb-board-meeting-pack-23-april-2026/), each holding the actual board pack PDF at /wp-content/uploads/YYYY/MM/Part-1-Essex-ICB-Board-Meeting-Pack-&lt;date&gt;.pdf. A crawler should fetch the publications index, follow links whose slug contains 'board-meeting-pack', then extract the wp-content/uploads PDF. Static fetch works (WordPress). Prefer the 'Part 1'/Part I public board pack PDF; ignore Part 2 (confidential) and any ICP/committee items. 2026 board packs live; older packs under earlier upload-month folders.</t>
         </is>
       </c>
       <c r="N21" t="b">
@@ -1938,17 +1938,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>/publications/essex-icb-board-meeting-pack-{DD-month-YYYY}/;wp-content/uploads/{YYYY}/{MM}/Part-1-Essex-ICB-Board-Meeting-Pack-*.pdf</t>
+          <t>wp-content/uploads/YYYY/MM/Part-1-Essex-ICB-Board-Meeting-Pack-&lt;date&gt;.pdf;/publications/essex-icb-board-meeting-pack-&lt;date&gt;/;Board Meeting Pack &lt;month&gt; &lt;year&gt;</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Integrated Care Partnership;ICP;Committee;Quality Committee;Finance Committee</t>
+          <t>Part-2;Part II;Integrated Care Partnership;ICP;committee;confidential</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Per-meeting sub-page off the publications list links a combined Part 1 Essex ICB Board pack PDF dated 23 April 2026.</t>
+          <t>Confirmed live 23 April 2026 board pack PDF reachable from the publications index via a dated sub-page.</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>The previously stored URL (/board-meetings/) is a generic meetings calendar that mixes ICP, primary-care sub-committees and place-based partnership boards, which is why the validator saw no ICB Board papers. The correct dedicated NEL ICB Board landing on the org's own domain is /about-us/about-nhs-north-east-london/our-board/board-meetings-and-papers/ (pattern C, wrong-url-fixed). It lists ICB Board meetings (every other month) as per-meeting sub-pages; each past meeting sub-page carries the dated combined board pack via /download-attachment/{id} links, and direct dated PDFs also exist under wp-content/uploads (e.g. NHS-North-East-London-ICB-Board-29.01.2025.pdf). Upcoming meetings show papers a minimum of five working days before; future-dated sub-pages have no PDFs yet. Filter to the NEL ICB Board only; skip ICP, sub-committees and partnership/place boards.</t>
+          <t>This is the correct ICB Board landing; it lists upcoming and past board meeting dates (bi-monthly: e.g. 25 Nov 2025, 28 Jan 2026, 31 Mar 2026), each linking to a per-meeting sub-page under /board-meetings/north-east-london-icb-board-meeting-&lt;n&gt;/ (older under /events/). The actual board pack PDF is attached on the meeting sub-page once papers are published (5 working days before), served either as /wp-content/uploads/YYYY/MM/NHS-North-East-London-ICB-Board-&lt;dd.mm.yyyy&gt;.pdf or via /download-attachment/&lt;id&gt;. Crawl: fetch the landing, follow each board-meeting sub-page, extract the ICB Board pack PDF. Static fetch works (WordPress). Future meetings show only a Teams joining email until papers go live. Prefer the single combined 'NHS North East London ICB Board &lt;date&gt;' pack; exclude borough/place sub-committee, committees-in-common, partnership board, and ICP items.</t>
         </is>
       </c>
       <c r="N23" t="b">
@@ -2092,17 +2092,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>/board-meetings/north-east-london-icb-board-meeting-{n}/;/download-attachment/{id};wp-content/uploads/{YYYY}/{MM}/NHS-North-East-London-ICB-Board-{DD.MM.YYYY}.pdf</t>
+          <t>wp-content/uploads/YYYY/MM/NHS-North-East-London-ICB-Board-DD.MM.YYYY.pdf;/board-meetings/north-east-london-icb-board-meeting-&lt;n&gt;/;/download-attachment/&lt;id&gt;</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Integrated Care Partnership;ICP;Sub-committee;Primary Care Contracts;Partnership Board;Health &amp; Wellbeing Board;Tower Hamlets Together</t>
+          <t>sub-committee;committees-in-common;partnership-board;ICP;place;borough;Health and Wellbeing Board;your-area</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Confirmed dated 2025 NEL ICB Board pack PDF (29 January 2025) on the org's own domain reachable from the board landing's per-meeting structure.</t>
+          <t>Confirmed live ICB Board pack PDF (29 Jan 2025) via the WordPress uploads pattern reached from per-meeting sub-pages.</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>West and North London ICB is a newly created organisation (live from 1 April 2026, formed from the North West London and North Central London ICBs), so the earliest ICB Board pack is the 1 April 2026 inaugural meeting. The stored board-meetings page is the correct ICB Board landing on the org's own domain, but the actual packs live in a JavaScript-rendered document library (pattern D, needs Playwright) under /how-we-are-run/policies-and-publications/navigate/479/2410, organised into per-meeting date folders. The 1 April 2026 folder (navigate/480/2410) was confirmed to contain the ICB Board meeting-in-public agenda plus supporting papers as download_file links on the org's own domain. The board landing page itself only lists meeting dates and notes papers appear about a week before each meeting, which is why the validator saw no papers. Filter to the W&amp;NL ICB Board; legacy NWL/NCL papers are linked off-site on partner ICB domains (nwlondonicb.nhs.uk, nclhealthandcare.org.uk) for pre-merger history.</t>
+          <t>Newly merged ICB (NHS North West London + NHS North Central London became NHS West and North London from 1 April 2026). The current board page is correct (rendered title 'West and North London ICB board meetings, agendas and papers') and is the canonical entry point. It lists future board dates (first board 17 Jun 2026, then 22 Jul 2026, 21 Oct 2026, 13 Jan 2027, 24 Mar 2027) and links to three document libraries: (1) its own new W+NL papers library at /how-we-are-run/policies-and-publications/navigate/479/2410 (a JS-rendered Joomla 'navigate' widget with dated folders per meeting), (2) legacy NCL papers at nclhealthandcare.org.uk, (3) legacy NWL papers at nwlondonicb.nhs.uk. Because the org only formed in April 2026, few/no current packs exist yet; new packs appear inside the dated folders of library 2410, which need rendering to expose PDF links. Crawl the navigate endpoint with a JS renderer, open each dated folder, take the combined board pack; for historical 2025 papers fall back to the two legacy domains. Exclude committee, primary care commissioning, and ICP/partnership material.</t>
         </is>
       </c>
       <c r="N26" t="b">
@@ -2295,27 +2295,27 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>/how-we-are-run/policies-and-publications/navigate/{folderId}/2410#document-library-2410;/download_file/{uuid}/293</t>
+          <t>/how-we-are-run/policies-and-publications/navigate/479/2410;navigate/479/2410/&lt;yyyy&gt;/&lt;mm&gt;/&lt;dd&gt;;dated 'Board meetings in public' folders;legacy: nwlondonicb.nhs.uk + nclhealthandcare.org.uk board papers</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>North West London ICB (legacy);North Central London ICB (legacy);Committee;ICP;Integrated Care Partnership</t>
+          <t>primary-care-commissioning-committee;Primary Care and Medicines Optimisation Committee;committee;ICP;partnership;public-meetings</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Playwright confirmed the 1 April 2026 W&amp;NL ICB Board meeting-in-public agenda and supporting papers as download_file links in the JS document library on the org's own domain.</t>
+          <t>Board page is the correct live landing and exposes a dated board-papers document library, but the PDFs sit inside a JS-rendered navigate widget (and legacy archives) so dated PDFs are not visible to a static fetch.</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>The previously stored board-papers parent page is an empty container that only shows two section headers ('NHS Thames Valley ICB' and 'Pre-NHS Thames Valley archive') with no documents, which is why the validator saw 347 chars of text and no papers. The correct live sub-page is /policies-and-documents/how-we-make-decisions/board-papers/nhs-thames-valley-icb (wrong-url-fixed, pattern A: dated combined pack on the landing), which lists the dated Thames Valley ICB Board papers, including 'Thames Valley ICB Board papers 20 May 2026' as a single combined ~2.8MB PDF served via a /file download path on the org's own domain. Skip the 'Pre-NHS Thames Valley archive' (legacy predecessor ICB papers) and any committee/ICP items.</t>
+          <t>This is the correct ICB Board papers sub-page; the validator's 822-char 'near-empty' reading was a false negative. A normal fetch renders the Joomla document table, which lists dated 'Thames Valley ICB Board papers &lt;date&gt;' entries, each downloadable as a single combined PDF via /policies-and-documents/how-we-make-decisions/board-papers/nhs-thames-valley-icb/&lt;id&gt;-thames-valley-icb-board-papers-&lt;date&gt;/file. The parent /board-papers page splits into 'NHS Thames Valley ICB' (current) and 'Pre-NHS Thames Valley archive' (older); use the former. Site resolves both with and without www. Crawl: fetch this sub-page, read the document table, follow each '.../file' link for the combined board papers PDF. Prefer the single 'ICB Board papers' combined PDF; exclude committee papers and any ICP items.</t>
         </is>
       </c>
       <c r="N29" t="b">
@@ -2520,17 +2520,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>/policies-and-documents/how-we-make-decisions/board-papers/nhs-thames-valley-icb/{id}-thames-valley-icb-board-papers-{dd-month-yyyy}/file</t>
+          <t>/policies-and-documents/how-we-make-decisions/board-papers/nhs-thames-valley-icb/&lt;id&gt;-thames-valley-icb-board-papers-&lt;date&gt;/file;Thames Valley ICB Board papers &lt;month&gt; &lt;year&gt;</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pre-NHS Thames Valley archive;Committee;ICP;Integrated Care Partnership</t>
+          <t>pre-nhs-thames-valley-archive;committee;ICP;Integrated Care Partnership</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>The nhs-thames-valley-icb sub-page lists a dated combined Thames Valley ICB Board pack PDF for 20 May 2026 on the org's own domain.</t>
+          <t>Confirmed live 20 May 2026 combined board papers PDF (2.81 MB) listed in the rendered document table on the current sub-page.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -1095,13 +1095,39 @@
           <t>Joint ICB Cluster Board with Birmingham and Solihull (QHL); cluster pack PDFs hosted on blackcountryics.org.uk under /application/files/</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Static-fetchable landing ('How we make decisions') with a single table of the formal public Board (the 'Joint ICB Cluster Board', which is Black Country ICB's board) meeting ~six times a year. Columns: Date / Venue / 'Link to papers (available following each meeting)'. Each dated row carries a 'Download papers for {date}' link to a combined papers PDF hosted on the legacy blackcountryics.org.uk domain (/download_file/view/{id}/475). Pattern A — no year folders or per-meeting sub-pages. Links only appear after each meeting has taken place, so future dates may have no link yet. This page lists ONLY the Board, so include all rows, but EXCLUDE the separately-listed committees (Audit and Governance, Joint Finance and Performance, Joint Quality, Joint Strategic Commissioning, Joint Transition, Joint Remuneration), the Place Committees, the AGM, and any ICP listing.</t>
+        </is>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Download papers for {DD Month Year};blackcountryics.org.uk/download_file/view/{id}/475;Joint ICB Cluster Board</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Audit and Governance Committee;Joint Finance and Performance Committee;Joint Quality Committee;Joint Strategic Commissioning Committee;Joint Transition Committee;Joint Remuneration Committee;Place Committees;Integrated Care Partnership;ICP;AGM</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Confirmed dated Board entries e.g. 'Download papers for 08 December 2025' (blackcountryics.org.uk/download_file/view/4017/475) and '11 May 2026' (/download_file/view/4236/475).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3037,7 +3063,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://devon.icb.nhs.uk/nhs-devon-board/meetings-and-papers/</t>
+          <t>https://swpboard.nhs.uk/board-meetings/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3060,13 +3086,39 @@
           <t>South West Peninsula joint board with Cornwall and IoS (QT6); cluster pack at swpboard.nhs.uk. Standalone Devon Board last met 28 August 2025.</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Pattern C + cluster (SW-PEN). NHS Devon and NHS Cornwall &amp; Isles of Scilly delegated their board functions to the joint South West Peninsula Board (Sept 2025); the joint board pack now lives on swpboard.nhs.uk, not devon.icb.nhs.uk (old /nhs-devon-board/meetings-and-papers/ is HTTP 404). Landing lists dated meetings (e.g. 16 Oct 2025, 27 Nov 2025, 29 Jan 2026) with a 'View the meeting papers and minutes' link per meeting leading to the combined pack PDF under /wp-content/uploads/YYYY/MM/ (e.g. SWPB-Public-29.01.2026-Meeting-Papers.pdf). This pack covers BOTH Devon and Cornwall &amp; IoS. URL fixed 2026-06-13.</t>
+        </is>
+      </c>
+      <c r="N37" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>SWPB-Public-DD.MM.YYYY-Meeting-Papers.pdf;South West Peninsula Board Meeting in Public;View the meeting papers and minutes</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>committee/sub-committee papers;minutes only;legacy devon.icb.nhs.uk standalone pages</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Joint SW Peninsula Board on swpboard.nhs.uk lists 2025/26 meetings incl 29 Jan 2026 (SWPB-Public-29.01.2026-Meeting-Papers.pdf); old devon.icb.nhs.uk path is 404.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
